--- a/output/2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dal 1984, specializzata in progettazione/costruzione/installazione/manutenzione impianti di aspirazione, filtrazione e depurazione aria industriale.</t>
+          <t>Dal 1984, specializzata in progettazione/costruzione/installazione/manutenzione impianti di aspirazione, filtrazione e depurazione aria industriale. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Impianti aspirazione centralizzati per saldatura/taglio/levigatura dal 1981. Telefono ed email non presenti nella lista originale, reperiti da fonte verificata (sito ufficiale).</t>
+          <t>Impianti aspirazione centralizzati per saldatura/taglio/levigatura dal 1981. Telefono ed email non presenti nella lista originale, reperiti da fonte verificata (sito ufficiale). [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -666,10 +666,9 @@
           <t>0543 795959</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Impianti aeraulici e di aspirazione civili/industriali dal 1993 (società dal 2003), certificazione ISO 9001:2015.</t>
+          <t>Impianti aeraulici e di aspirazione civili/industriali dal 1993 (società dal 2003), certificazione ISO 9001:2015. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -704,10 +703,9 @@
           <t>0541 827127 / 0541 957680</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alcune fonti (europages) riportano la forma giuridica come S.n.c. anziché S.r.l.: da verificare ulteriormente la ragione sociale esatta.</t>
+          <t>Alcune fonti (europages) riportano la forma giuridica come S.n.c. anziché S.r.l.: da verificare ulteriormente la ragione sociale esatta. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -742,10 +740,9 @@
           <t>0536 071051</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oltre 35 anni di esperienza in installazione impianti aspirazione/filtrazione polveri e fumi industriali; opera in tutta l'Emilia-Romagna.</t>
+          <t>Oltre 35 anni di esperienza in installazione impianti aspirazione/filtrazione polveri e fumi industriali; opera in tutta l'Emilia-Romagna. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -775,7 +772,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>commerciale@lnrecology.com</t>
@@ -798,7 +794,6 @@
           <t>Nova Airbank S.n.c. di Cipelli Stefano e C.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>PC - Rottofreno</t>
@@ -814,7 +809,6 @@
           <t>0523 762337</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Attività di rappresentanza/commercio macchinari aria compressa e impianti di aspirazione (profilo idoneo come distributore). Fonti diverse riportano indirizzi leggermente diversi, tutti a Rottofreno; telefono confermato univoco.</t>
@@ -852,10 +846,9 @@
           <t>0543 725482</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oltre 30 anni di esperienza in progettazione/installazione impianti di filtrazione e trattamento aria industriale.</t>
+          <t>Oltre 30 anni di esperienza in progettazione/installazione impianti di filtrazione e trattamento aria industriale. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -870,7 +863,6 @@
           <t>Tecno Aria S.r.l.</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>PR - Parma</t>
@@ -893,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nessun sito web dedicato con dominio proprio confermato (presenza principale su pagina Google Business); email e telefono confermati da fonti multiple.</t>
+          <t>Nessun sito web dedicato con dominio proprio confermato (presenza principale su pagina Google Business); email e telefono confermati da fonti multiple. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -928,10 +920,9 @@
           <t>0521 291323 / 348 2258501</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Telefono non presente nella lista originale, reperito da fonte verificata (paginegialle/ufficiocamerale).</t>
+          <t>Telefono non presente nella lista originale, reperito da fonte verificata (paginegialle/ufficiocamerale). [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -966,7 +957,6 @@
           <t>0524 97509</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Carpenteria metallica e impianti meccanici industriali, incluso montaggio impianti di aspirazione (Parma/Piacenza). Telefono reperito da fonte esterna, non presente nella lista originale.</t>
@@ -1011,7 +1001,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Azienda diversificata (elettromeccanica generale, rivenditore STIGA) attiva anche da oltre 30 anni nell'installazione/manutenzione di impianti di aspirazione industriale.</t>
+          <t>Azienda diversificata (elettromeccanica generale, rivenditore STIGA) attiva anche da oltre 30 anni nell'installazione/manutenzione di impianti di aspirazione industriale. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1046,7 +1036,6 @@
           <t>347 318 2750 / 338 219 0683</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Il sito principale cemgroupsrl.com verte su pompe di lubrificazione automatica; la divisione aspirazione industriale è documentata sul dominio separato aspirazione-industriale.it. Email non reperita.</t>
@@ -1079,8 +1068,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Oltre 30 anni di esperienza, oltre 700 impianti realizzati; opera anche fuori regione. Contatti diretti non reperiti nelle fonti consultate.</t>
@@ -1209,7 +1196,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Vendita, assistenza e noleggio di impianti industriali di aspirazione fumi di saldatura e filtrazione aria.</t>
+          <t>Vendita, assistenza e noleggio di impianti industriali di aspirazione fumi di saldatura e filtrazione aria. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1251,7 +1238,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Impiantistica meccanica industriale chiavi in mano, categorizzata anche sotto "impianti di aspirazione" nelle directory di settore per Ferrara.</t>
+          <t>Impiantistica meccanica industriale chiavi in mano, categorizzata anche sotto "impianti di aspirazione" nelle directory di settore per Ferrara. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1328,7 +1315,6 @@
           <t>0522 577789</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Progettazione meccanica industriale, incluso impianti di aspirazione e pulizia ambienti industriali. Trovate solo email personali, omesse per policy anti-invenzione dati.</t>
@@ -1373,7 +1359,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione su misura e progettazione filtri industriali. Alcune directory riportano anche una sede/referenza secondaria a Sorbolo a Levante (RE), da verificare se si tratti di filiale.</t>
+          <t>Impianti di aspirazione su misura e progettazione filtri industriali. Alcune directory riportano anche una sede/referenza secondaria a Sorbolo a Levante (RE), da verificare se si tratti di filiale. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
